--- a/data/2025/42-bucuresti/179132-bucuresti/budget_file.xlsx
+++ b/data/2025/42-bucuresti/179132-bucuresti/budget_file.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -514,37 +514,41 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -554,7 +558,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -564,10 +568,176 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7184ec69989ee89faf565942</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>c06e76af14c3013dfd884966828591737a32a13f522632071d4ca6c416ee3cfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL GENERAL CENTRALIZAT AL MUNICIPIULUI BUCURE</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>general, pag. 1-4, 0 linii</t>
         </is>

--- a/data/2025/42-bucuresti/179132-bucuresti/budget_file.xlsx
+++ b/data/2025/42-bucuresti/179132-bucuresti/budget_file.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Probleme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sumar calitate" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BG Date" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Probleme" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sumar calitate" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +45,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +70,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -428,7 +456,1994 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:Q38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cod functional</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Denumire</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rand</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pag.</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL 2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bugetul local</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. venituri proprii si subventii</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. integral venituri proprii</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Imprumuturi externe</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Imprumuturi interne</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fonduri externe nerambursabile</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Transferuri intre bugete</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Total buget general</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Sursa</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Probleme</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'L' in column inst_venituri_proprii_subventii; unparseable cell '.j' in column inst_integral_venituri_proprii; unparseable cell '::,' in column imprumuturi_interne; unparseable cell '1~1+L+,j+4+::,+o' in column total_2025; unparseable cell '!:l~ , -o' in column total_general</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>VENITURI TOTAL (rd.02+18+19+20+23)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" s="6" t="n">
+        <v>13245406.79</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>7789331.79</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1048932</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>3238690</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>1080047</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>80550</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>7856</v>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <v>12021613.79</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Venituri curente (rd.03+17)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
+        <v>7529868.15</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>5710272.15</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>113495</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1706101</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n">
+        <v>7529868.15</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Venituri fiscale (rd.04+06+09+10+11+16)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="4" t="n">
+        <v>4539963.89</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>4539963.89</v>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n">
+        <v>4539963.89</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Impozit pe venit, profit si castiguri din capital de la persoane juridice, din care:</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column bugetul_local; unparseable cell 'o.oa' in column inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>05.02</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Impozit pe profit</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_integral_venituri_proprii; unparseable cell 'O.DO' in column imprumuturi_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Impozit pe venit, profit si castiguri din capital de la persoane fizice, din care:</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="4" t="n">
+        <v>4364289</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>4364289</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n">
+        <v>4364289</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Impozitul pe veniturile din transferul proprietatilor imobiliare din patrimoniul personal *)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>42049</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>42049</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n">
+        <v>42049</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Cote si sume defalcate din impozitul pe venit</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="4" t="n">
+        <v>4322240</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>4322240</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n">
+        <v>4322240</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Alte impozite pe venit, profit si castiguri din capital</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Impozite şi taxe pe proprietate</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (39%): 'Impozite şi taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Impozite si taxe pe bunuri si servicii (rd.12 la rd.15)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="4" t="n">
+        <v>162469.89</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>162469.89</v>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n">
+        <v>162469.89</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Sume defalcate din TVA</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="4" t="n">
+        <v>79871</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>79871</v>
+      </c>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n">
+        <v>79871</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Alte impozite si taxe generale pe bunuri si servicii</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column total_2025; unparseable cell 'o.oa' in column total_general</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Taxe pe servicii specifice</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column imprumuturi_interne; unparseable cell 'O.DO' in column total_2025; unparseable cell 'o.o a' in column total_general</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Taxe pe utilizarea bunurilor, autorizarea utilizarii bunurilor sau pe desfasurarea de activitati</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" s="6" t="n">
+        <v>82598.89</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>82598.89</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>82598.89</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Alte impozite si taxe fiscale</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="4" t="n">
+        <v>13205</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>13205</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n">
+        <v>13205</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column fonduri_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Venituri nefiscale</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>2989904.26</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1170308.26</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>113495</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>1706101</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>2989904.26</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Venituri din capital</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>338677.78</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>338649.78</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>338677.78</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Operatiuni financiare</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="4" t="n">
+        <v>1520830</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>55678</v>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n">
+        <v>298492</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>1080047</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>80550</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>6063</v>
+      </c>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n">
+        <v>1520830</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Subvenţii (rd.21 +22)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>3455089.79</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1285737.79</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>935393</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>1233959</v>
+      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>2231296.79</v>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_externe; unparseable cell 'o.oa' in column imprumuturi_interne; name mismatch vs nomenclator (29%): 'Subvenţii (rd.21 +22)' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Subvenţii de la bugetul de stat</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="4" t="n">
+        <v>1254496</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1205818</v>
+      </c>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n">
+        <v>48678</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n">
+        <v>1254496</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Subventii de la alte administratii</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="4" t="n">
+        <v>2200593.79</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>79919.78999999999</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>935393</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>1185281</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>976800.79</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_interne; unparseable cell 'O.DO' in column fonduri_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Sume primite de la UE în contul platilor efectuate</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>23</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" s="6" t="n">
+        <v>400941.07</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>398994.07</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>1793</v>
+      </c>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n">
+        <v>400941.07</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>CHELTUIELI· TOTAL (rd.25+36+37+40+41)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>13245406.79</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>7789331.79</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1048932</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>3238690</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>1080047</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>80550</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>7856</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>12021613.79</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Cheltuieli curente (rd.25 la rd.33)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>11033068.79</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>6818324.79</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>981856</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>3045032</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>7856</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>9809275.789999999</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Cheltuieli de personal</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="4" t="n">
+        <v>2353063</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>465101</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>399145</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>1488817</v>
+      </c>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n">
+        <v>2353063</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_externe; unparseable cell 'O.DO' in column fonduri_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Bunuri si servicii</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="4" t="n">
+        <v>2584856</v>
+      </c>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n">
+        <v>512199</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>1490900</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n">
+        <v>2584856</v>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "' 581,757.00" in column bugetul_local</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Dobanzi</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="4" t="n">
+        <v>309059</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>309059</v>
+      </c>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n">
+        <v>309059</v>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii; unparseable cell 'O.DO' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Subventii</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="4" t="n">
+        <v>2725130.11</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>2625130.11</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n">
+        <v>2725130.11</v>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Fonduri de rezerva</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Transferuri intre unitati ale administratiei publice</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>31</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" s="6" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>1223793</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Alte transferuri</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>32</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" s="6" t="n">
+        <v>39391</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>39391</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="6" t="n">
+        <v>39391</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Proiecte cu finantare din Fonduri externe nerambursabile postaderare</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>33</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" s="6" t="n">
+        <v>867555.3100000001</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>779545.3100000001</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>7856</v>
+      </c>
+      <c r="N35" s="6" t="n"/>
+      <c r="O35" s="6" t="n">
+        <v>867555.3100000001</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Asistenta sociala</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>34</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" s="6" t="n">
+        <v>405475.37</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>405475.37</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="6" t="n">
+        <v>405475.37</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Alte cheltuieli</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="4" t="n">
+        <v>263041</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>240344</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>6198</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>16499</v>
+      </c>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n">
+        <v>263041</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O .DO' in column imprumuturi_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Proiecte cu finantare din sumele reprezentând asistenta financiara nerambursabila aferenta PNRR</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>36</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" s="6" t="n">
+        <v>155254</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>106576</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>48678</v>
+      </c>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="6" t="n">
+        <v>155254</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -471,12 +2486,912 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'L' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>unparseable cell '.j' in column inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>imprumuturi_interne</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>unparseable cell '::,' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>total_2025</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>unparseable cell '1~1+L+,j+4+::,+o' in column total_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>total_general</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>unparseable cell '!:l~ , -o' in column total_general</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>bugetul_local</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column bugetul_local</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>imprumuturi_externe</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column inst_integral_venituri_proprii</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>imprumuturi_interne</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (39%): 'Impozite şi taxe pe proprietate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>total_2025</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column total_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>total_general</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column total_general</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>imprumuturi_interne</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>total_2025</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column total_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>total_general</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.o a' in column total_general</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>fonduri_externe</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column fonduri_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>imprumuturi_externe</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>imprumuturi_interne</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>unparseable cell 'o.oa' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (29%): 'Subvenţii (rd.21 +22)' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>imprumuturi_interne</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>fonduri_externe</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column fonduri_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>imprumuturi_externe</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>fonduri_externe</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column fonduri_externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>bugetul_local</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>unparseable cell "' 581,757.00" in column bugetul_local</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column inst_venituri_proprii_subventii</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>imprumuturi_interne</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>imprumuturi_interne</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O.DO' in column imprumuturi_interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (28%): 'Fonduri de rezerva' vs 'TITLUL III DOBANZI'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>imprumuturi_externe</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>unparseable cell 'O .DO' in column imprumuturi_externe</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -490,7 +3405,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Fisier</t>
         </is>
@@ -502,17 +3417,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Metrica de calitate</t>
         </is>
@@ -524,7 +3439,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Recall masurat</t>
         </is>
@@ -536,7 +3451,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Documente</t>
         </is>
@@ -546,17 +3461,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Linii strict verificate</t>
         </is>
@@ -566,7 +3481,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>% linii strict verificate</t>
         </is>
@@ -576,37 +3491,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Celule numerice</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Celule numerice strict verificate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>% celule numerice strict verificate</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Pagini asteptate</t>
         </is>
@@ -616,7 +3531,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Pagini selectate</t>
         </is>
@@ -626,7 +3541,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Pagini procesate</t>
         </is>
@@ -636,7 +3551,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>PDF complet</t>
         </is>
@@ -648,7 +3563,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Linii fara probleme</t>
         </is>
@@ -658,7 +3573,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>% curat</t>
         </is>
@@ -668,27 +3583,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Erori</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Avertismente</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Informatii</t>
         </is>
@@ -698,7 +3613,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Schema publicare</t>
         </is>
@@ -708,19 +3623,19 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7184ec69989ee89faf565942</t>
+          <t>fa06bc12c192e4d36039d8de</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>SHA-256 PDF sursa</t>
         </is>
@@ -732,14 +3647,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>— BUGETUL GENERAL CENTRALIZAT AL MUNICIPIULUI BUCURE</t>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>— BUGETUL GENERAL CENTRALIZAT AL MUNICIPIULUI PE ANUL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>general, pag. 1-4, 0 linii</t>
+          <t>general, pag. 1-4, 37 linii</t>
         </is>
       </c>
     </row>
